--- a/Data terbaru dip/X5 Persentase Perempuan Lulus Wajib Belajar/X6 Jumlah Lulus 2023.xlsx
+++ b/Data terbaru dip/X5 Persentase Perempuan Lulus Wajib Belajar/X6 Jumlah Lulus 2023.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KULIAH\Project\womanguard-index-surabaya\Data terbaru dip\X5 Persentase Perempuan Lulus Wajib Belajar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5922F374-C027-4CC2-BDBC-3737A419A6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8309BD02-8637-4C5B-B8A5-2F51AC26C7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17580" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pendidikan 2022" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
   <si>
     <t>Data Pendidikan Menurut Kecamatan dan Jenis Kelamin di Kota Surabaya (Tahun Berjalan 2022)</t>
   </si>
@@ -67,10 +78,6 @@
 Doctor</t>
   </si>
   <si>
-    <t>Jumlah
-Total</t>
-  </si>
-  <si>
     <t>Laki-Laki
 Male</t>
   </si>
@@ -170,16 +177,13 @@
   </si>
   <si>
     <t>Pakal</t>
-  </si>
-  <si>
-    <t>Kota Surabaya</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,14 +214,8 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,14 +240,8 @@
         <bgColor rgb="FFF2F7F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E0B4"/>
-        <bgColor rgb="FFC6E0B4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -272,26 +264,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -307,12 +284,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -621,134 +592,129 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="21" width="13" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:21" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="9" t="s">
+      <c r="G3" s="8"/>
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="9" t="s">
+      <c r="I3" s="8"/>
+      <c r="J3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="9" t="s">
+      <c r="K3" s="8"/>
+      <c r="L3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="9" t="s">
+      <c r="M3" s="8"/>
+      <c r="N3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="9" t="s">
+      <c r="O3" s="8"/>
+      <c r="P3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="9" t="s">
+      <c r="Q3" s="8"/>
+      <c r="R3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="10"/>
-      <c r="T3" s="9" t="s">
+      <c r="S3" s="8"/>
+      <c r="T3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="10"/>
-      <c r="V3" s="9" t="s">
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" spans="1:21" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V4" s="10"/>
-    </row>
-    <row r="5" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="B5" s="4">
         <v>9434</v>
@@ -810,14 +776,10 @@
       <c r="U5" s="4">
         <v>15</v>
       </c>
-      <c r="V5" s="4">
-        <f t="shared" ref="V5:V35" si="0">SUM(B5:U5)</f>
-        <v>74931</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="6">
         <v>6210</v>
@@ -879,14 +841,10 @@
       <c r="U6" s="6">
         <v>18</v>
       </c>
-      <c r="V6" s="6">
-        <f t="shared" si="0"/>
-        <v>53639</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="4">
         <v>5780</v>
@@ -948,14 +906,10 @@
       <c r="U7" s="4">
         <v>21</v>
       </c>
-      <c r="V7" s="4">
-        <f t="shared" si="0"/>
-        <v>43617</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="6">
         <v>10344</v>
@@ -1017,14 +971,10 @@
       <c r="U8" s="6">
         <v>23</v>
       </c>
-      <c r="V8" s="6">
-        <f t="shared" si="0"/>
-        <v>79559</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="4">
         <v>6836</v>
@@ -1086,14 +1036,10 @@
       <c r="U9" s="4">
         <v>18</v>
       </c>
-      <c r="V9" s="4">
-        <f t="shared" si="0"/>
-        <v>58695</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="6">
         <v>7557</v>
@@ -1155,14 +1101,10 @@
       <c r="U10" s="6">
         <v>23</v>
       </c>
-      <c r="V10" s="6">
-        <f t="shared" si="0"/>
-        <v>60535</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="4">
         <v>14668</v>
@@ -1224,14 +1166,10 @@
       <c r="U11" s="4">
         <v>68</v>
       </c>
-      <c r="V11" s="4">
-        <f t="shared" si="0"/>
-        <v>120067</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="6">
         <v>16730</v>
@@ -1293,14 +1231,10 @@
       <c r="U12" s="6">
         <v>98</v>
       </c>
-      <c r="V12" s="6">
-        <f t="shared" si="0"/>
-        <v>113876</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="4">
         <v>12194</v>
@@ -1362,14 +1296,10 @@
       <c r="U13" s="4">
         <v>55</v>
       </c>
-      <c r="V13" s="4">
-        <f t="shared" si="0"/>
-        <v>86824</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="6">
         <v>15953</v>
@@ -1431,14 +1361,10 @@
       <c r="U14" s="6">
         <v>35</v>
       </c>
-      <c r="V14" s="6">
-        <f t="shared" si="0"/>
-        <v>133900</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="4">
         <v>19283</v>
@@ -1500,14 +1426,10 @@
       <c r="U15" s="4">
         <v>19</v>
       </c>
-      <c r="V15" s="4">
-        <f t="shared" si="0"/>
-        <v>155559</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" s="6">
         <v>7799</v>
@@ -1569,14 +1491,10 @@
       <c r="U16" s="6">
         <v>14</v>
       </c>
-      <c r="V16" s="6">
-        <f t="shared" si="0"/>
-        <v>59293</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="4">
         <v>9742</v>
@@ -1638,14 +1556,10 @@
       <c r="U17" s="4">
         <v>13</v>
       </c>
-      <c r="V17" s="4">
-        <f t="shared" si="0"/>
-        <v>74224</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="6">
         <v>10117</v>
@@ -1707,14 +1621,10 @@
       <c r="U18" s="6">
         <v>5</v>
       </c>
-      <c r="V18" s="6">
-        <f t="shared" si="0"/>
-        <v>63017</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="4">
         <v>8544</v>
@@ -1776,14 +1686,10 @@
       <c r="U19" s="4">
         <v>5</v>
       </c>
-      <c r="V19" s="4">
-        <f t="shared" si="0"/>
-        <v>66796</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="6">
         <v>12851</v>
@@ -1845,14 +1751,10 @@
       <c r="U20" s="6">
         <v>5</v>
       </c>
-      <c r="V20" s="6">
-        <f t="shared" si="0"/>
-        <v>91784</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="4">
         <v>15111</v>
@@ -1914,14 +1816,10 @@
       <c r="U21" s="4">
         <v>9</v>
       </c>
-      <c r="V21" s="4">
-        <f t="shared" si="0"/>
-        <v>104271</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="6">
         <v>32401</v>
@@ -1983,14 +1881,10 @@
       <c r="U22" s="6">
         <v>5</v>
       </c>
-      <c r="V22" s="6">
-        <f t="shared" si="0"/>
-        <v>199548</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="4">
         <v>11176</v>
@@ -2052,14 +1946,10 @@
       <c r="U23" s="4">
         <v>7</v>
       </c>
-      <c r="V23" s="4">
-        <f t="shared" si="0"/>
-        <v>98484</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="6">
         <v>7239</v>
@@ -2121,14 +2011,10 @@
       <c r="U24" s="6">
         <v>6</v>
       </c>
-      <c r="V24" s="6">
-        <f t="shared" si="0"/>
-        <v>58601</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="4">
         <v>38355</v>
@@ -2190,14 +2076,10 @@
       <c r="U25" s="4">
         <v>32</v>
       </c>
-      <c r="V25" s="4">
-        <f t="shared" si="0"/>
-        <v>226136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="6">
         <v>28414</v>
@@ -2259,14 +2141,10 @@
       <c r="U26" s="6">
         <v>3</v>
       </c>
-      <c r="V26" s="6">
-        <f t="shared" si="0"/>
-        <v>177561</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="4">
         <v>7190</v>
@@ -2328,14 +2206,10 @@
       <c r="U27" s="4">
         <v>4</v>
       </c>
-      <c r="V27" s="4">
-        <f t="shared" si="0"/>
-        <v>46350</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="6">
         <v>13332</v>
@@ -2397,14 +2271,10 @@
       <c r="U28" s="6">
         <v>1</v>
       </c>
-      <c r="V28" s="6">
-        <f t="shared" si="0"/>
-        <v>92832</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="4">
         <v>27462</v>
@@ -2466,14 +2336,10 @@
       <c r="U29" s="4">
         <v>4</v>
       </c>
-      <c r="V29" s="4">
-        <f t="shared" si="0"/>
-        <v>181226</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="6">
         <v>11005</v>
@@ -2535,14 +2401,10 @@
       <c r="U30" s="6">
         <v>1</v>
       </c>
-      <c r="V30" s="6">
-        <f t="shared" si="0"/>
-        <v>74810</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="4">
         <v>12781</v>
@@ -2604,14 +2466,10 @@
       <c r="U31" s="4">
         <v>8</v>
       </c>
-      <c r="V31" s="4">
-        <f t="shared" si="0"/>
-        <v>97707</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="6">
         <v>19597</v>
@@ -2673,14 +2531,10 @@
       <c r="U32" s="6">
         <v>5</v>
       </c>
-      <c r="V32" s="6">
-        <f t="shared" si="0"/>
-        <v>114674</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" s="4">
         <v>8960</v>
@@ -2742,14 +2596,10 @@
       <c r="U33" s="4">
         <v>0</v>
       </c>
-      <c r="V33" s="4">
-        <f t="shared" si="0"/>
-        <v>47437</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" s="6">
         <v>9084</v>
@@ -2811,14 +2661,10 @@
       <c r="U34" s="6">
         <v>3</v>
       </c>
-      <c r="V34" s="6">
-        <f t="shared" si="0"/>
-        <v>71133</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="4">
         <v>8243</v>
@@ -2880,105 +2726,11 @@
       <c r="U35" s="4">
         <v>5</v>
       </c>
-      <c r="V35" s="4">
-        <f t="shared" si="0"/>
-        <v>60877</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="8">
-        <f t="shared" ref="B36:V36" si="1">SUM(B5:B35)</f>
-        <v>424392</v>
-      </c>
-      <c r="C36" s="8">
-        <f t="shared" si="1"/>
-        <v>401890</v>
-      </c>
-      <c r="D36" s="8">
-        <f t="shared" si="1"/>
-        <v>109824</v>
-      </c>
-      <c r="E36" s="8">
-        <f t="shared" si="1"/>
-        <v>106398</v>
-      </c>
-      <c r="F36" s="8">
-        <f t="shared" si="1"/>
-        <v>178418</v>
-      </c>
-      <c r="G36" s="8">
-        <f t="shared" si="1"/>
-        <v>232325</v>
-      </c>
-      <c r="H36" s="8">
-        <f t="shared" si="1"/>
-        <v>168789</v>
-      </c>
-      <c r="I36" s="8">
-        <f t="shared" si="1"/>
-        <v>182182</v>
-      </c>
-      <c r="J36" s="8">
-        <f t="shared" si="1"/>
-        <v>419542</v>
-      </c>
-      <c r="K36" s="8">
-        <f t="shared" si="1"/>
-        <v>393901</v>
-      </c>
-      <c r="L36" s="8">
-        <f t="shared" si="1"/>
-        <v>7610</v>
-      </c>
-      <c r="M36" s="8">
-        <f t="shared" si="1"/>
-        <v>9291</v>
-      </c>
-      <c r="N36" s="8">
-        <f t="shared" si="1"/>
-        <v>16780</v>
-      </c>
-      <c r="O36" s="8">
-        <f t="shared" si="1"/>
-        <v>23601</v>
-      </c>
-      <c r="P36" s="8">
-        <f t="shared" si="1"/>
-        <v>141871</v>
-      </c>
-      <c r="Q36" s="8">
-        <f t="shared" si="1"/>
-        <v>149016</v>
-      </c>
-      <c r="R36" s="8">
-        <f t="shared" si="1"/>
-        <v>11599</v>
-      </c>
-      <c r="S36" s="8">
-        <f t="shared" si="1"/>
-        <v>9016</v>
-      </c>
-      <c r="T36" s="8">
-        <f t="shared" si="1"/>
-        <v>990</v>
-      </c>
-      <c r="U36" s="8">
-        <f t="shared" si="1"/>
-        <v>528</v>
-      </c>
-      <c r="V36" s="8">
-        <f t="shared" si="1"/>
-        <v>2987963</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="V3:V4"/>
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="T3:U3"/>
